--- a/import-templates/DA_Import_Template.xlsx
+++ b/import-templates/DA_Import_Template.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>412345678901</t>
+          <t>4123456789010001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
